--- a/artfynd/A 32609-2019 artfynd.xlsx
+++ b/artfynd/A 32609-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819486</v>
+        <v>119819491</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713196</v>
+        <v>713241</v>
       </c>
       <c r="R2" t="n">
-        <v>7163164</v>
+        <v>7163150</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819487</v>
+        <v>119819481</v>
       </c>
       <c r="B3" t="n">
         <v>91834</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713218</v>
+        <v>713079</v>
       </c>
       <c r="R3" t="n">
-        <v>7163161</v>
+        <v>7163036</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819490</v>
+        <v>119819479</v>
       </c>
       <c r="B5" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713250</v>
+        <v>713072</v>
       </c>
       <c r="R5" t="n">
-        <v>7163149</v>
+        <v>7163032</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819489</v>
+        <v>119819478</v>
       </c>
       <c r="B6" t="n">
-        <v>91463</v>
+        <v>91856</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713257</v>
+        <v>713071</v>
       </c>
       <c r="R6" t="n">
-        <v>7163139</v>
+        <v>7163031</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819479</v>
+        <v>119819477</v>
       </c>
       <c r="B7" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713072</v>
+        <v>713041</v>
       </c>
       <c r="R7" t="n">
-        <v>7163032</v>
+        <v>7162983</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819491</v>
+        <v>119819482</v>
       </c>
       <c r="B8" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713241</v>
+        <v>713088</v>
       </c>
       <c r="R8" t="n">
-        <v>7163150</v>
+        <v>7163047</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819481</v>
+        <v>119819484</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,26 +1579,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713079</v>
+        <v>713213</v>
       </c>
       <c r="R10" t="n">
-        <v>7163036</v>
+        <v>7163095</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819484</v>
+        <v>119819489</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
+        <v>91463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713213</v>
+        <v>713257</v>
       </c>
       <c r="R11" t="n">
-        <v>7163095</v>
+        <v>7163139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819477</v>
+        <v>119819490</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>89252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713041</v>
+        <v>713250</v>
       </c>
       <c r="R12" t="n">
-        <v>7162983</v>
+        <v>7163149</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819478</v>
+        <v>119819487</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713071</v>
+        <v>713218</v>
       </c>
       <c r="R13" t="n">
-        <v>7163031</v>
+        <v>7163161</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819482</v>
+        <v>119819486</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713088</v>
+        <v>713196</v>
       </c>
       <c r="R14" t="n">
-        <v>7163047</v>
+        <v>7163164</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 32609-2019 artfynd.xlsx
+++ b/artfynd/A 32609-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819491</v>
+        <v>119819486</v>
       </c>
       <c r="B2" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713241</v>
+        <v>713196</v>
       </c>
       <c r="R2" t="n">
-        <v>7163150</v>
+        <v>7163164</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819481</v>
+        <v>119819477</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713079</v>
+        <v>713041</v>
       </c>
       <c r="R3" t="n">
-        <v>7163036</v>
+        <v>7162983</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819485</v>
+        <v>119819482</v>
       </c>
       <c r="B4" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713190</v>
+        <v>713088</v>
       </c>
       <c r="R4" t="n">
-        <v>7163199</v>
+        <v>7163047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819479</v>
+        <v>119819483</v>
       </c>
       <c r="B5" t="n">
         <v>91856</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713072</v>
+        <v>713186</v>
       </c>
       <c r="R5" t="n">
-        <v>7163032</v>
+        <v>7163050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819478</v>
+        <v>119819490</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713071</v>
+        <v>713250</v>
       </c>
       <c r="R6" t="n">
-        <v>7163031</v>
+        <v>7163149</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819477</v>
+        <v>119819489</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713041</v>
+        <v>713257</v>
       </c>
       <c r="R7" t="n">
-        <v>7162983</v>
+        <v>7163139</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819482</v>
+        <v>119819484</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713088</v>
+        <v>713213</v>
       </c>
       <c r="R8" t="n">
-        <v>7163047</v>
+        <v>7163095</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819483</v>
+        <v>119819481</v>
       </c>
       <c r="B9" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713186</v>
+        <v>713079</v>
       </c>
       <c r="R9" t="n">
-        <v>7163050</v>
+        <v>7163036</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819484</v>
+        <v>119819485</v>
       </c>
       <c r="B10" t="n">
         <v>91856</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713213</v>
+        <v>713190</v>
       </c>
       <c r="R10" t="n">
-        <v>7163095</v>
+        <v>7163199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819489</v>
+        <v>119819478</v>
       </c>
       <c r="B11" t="n">
-        <v>91463</v>
+        <v>91856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713257</v>
+        <v>713071</v>
       </c>
       <c r="R11" t="n">
-        <v>7163139</v>
+        <v>7163031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819490</v>
+        <v>119819487</v>
       </c>
       <c r="B12" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713250</v>
+        <v>713218</v>
       </c>
       <c r="R12" t="n">
-        <v>7163149</v>
+        <v>7163161</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819487</v>
+        <v>119819491</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713218</v>
+        <v>713241</v>
       </c>
       <c r="R13" t="n">
-        <v>7163161</v>
+        <v>7163150</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819486</v>
+        <v>119819479</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713196</v>
+        <v>713072</v>
       </c>
       <c r="R14" t="n">
-        <v>7163164</v>
+        <v>7163032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 32609-2019 artfynd.xlsx
+++ b/artfynd/A 32609-2019 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819477</v>
+        <v>119819482</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713041</v>
+        <v>713088</v>
       </c>
       <c r="R3" t="n">
-        <v>7162983</v>
+        <v>7163047</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819482</v>
+        <v>119819477</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713088</v>
+        <v>713041</v>
       </c>
       <c r="R4" t="n">
-        <v>7163047</v>
+        <v>7162983</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819490</v>
+        <v>119819489</v>
       </c>
       <c r="B6" t="n">
-        <v>89252</v>
+        <v>91463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4745</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713250</v>
+        <v>713257</v>
       </c>
       <c r="R6" t="n">
-        <v>7163149</v>
+        <v>7163139</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819489</v>
+        <v>119819490</v>
       </c>
       <c r="B7" t="n">
-        <v>91463</v>
+        <v>89252</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4745</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713257</v>
+        <v>713250</v>
       </c>
       <c r="R7" t="n">
-        <v>7163139</v>
+        <v>7163149</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 32609-2019 artfynd.xlsx
+++ b/artfynd/A 32609-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819486</v>
+        <v>119819483</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713196</v>
+        <v>713186</v>
       </c>
       <c r="R2" t="n">
-        <v>7163164</v>
+        <v>7163050</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819482</v>
+        <v>119819486</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713088</v>
+        <v>713196</v>
       </c>
       <c r="R3" t="n">
-        <v>7163047</v>
+        <v>7163164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819477</v>
+        <v>119819478</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713041</v>
+        <v>713071</v>
       </c>
       <c r="R4" t="n">
-        <v>7162983</v>
+        <v>7163031</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819483</v>
+        <v>119819489</v>
       </c>
       <c r="B5" t="n">
-        <v>91856</v>
+        <v>91463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713186</v>
+        <v>713257</v>
       </c>
       <c r="R5" t="n">
-        <v>7163050</v>
+        <v>7163139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819489</v>
+        <v>119819487</v>
       </c>
       <c r="B6" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713257</v>
+        <v>713218</v>
       </c>
       <c r="R6" t="n">
-        <v>7163139</v>
+        <v>7163161</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819490</v>
+        <v>119819477</v>
       </c>
       <c r="B7" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713250</v>
+        <v>713041</v>
       </c>
       <c r="R7" t="n">
-        <v>7163149</v>
+        <v>7162983</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819484</v>
+        <v>119819482</v>
       </c>
       <c r="B8" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713213</v>
+        <v>713088</v>
       </c>
       <c r="R8" t="n">
-        <v>7163095</v>
+        <v>7163047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819481</v>
+        <v>119819484</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713079</v>
+        <v>713213</v>
       </c>
       <c r="R9" t="n">
-        <v>7163036</v>
+        <v>7163095</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819478</v>
+        <v>119819481</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,26 +1690,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713071</v>
+        <v>713079</v>
       </c>
       <c r="R11" t="n">
-        <v>7163031</v>
+        <v>7163036</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819487</v>
+        <v>119819490</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713218</v>
+        <v>713250</v>
       </c>
       <c r="R12" t="n">
-        <v>7163161</v>
+        <v>7163149</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819491</v>
+        <v>119819479</v>
       </c>
       <c r="B13" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713241</v>
+        <v>713072</v>
       </c>
       <c r="R13" t="n">
-        <v>7163150</v>
+        <v>7163032</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819479</v>
+        <v>119819491</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713072</v>
+        <v>713241</v>
       </c>
       <c r="R14" t="n">
-        <v>7163032</v>
+        <v>7163150</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 32609-2019 artfynd.xlsx
+++ b/artfynd/A 32609-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819483</v>
+        <v>119819481</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713186</v>
+        <v>713079</v>
       </c>
       <c r="R2" t="n">
-        <v>7163050</v>
+        <v>7163036</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819486</v>
+        <v>119819490</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>89269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713196</v>
+        <v>713250</v>
       </c>
       <c r="R3" t="n">
-        <v>7163164</v>
+        <v>7163149</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>119819478</v>
       </c>
       <c r="B4" t="n">
-        <v>91856</v>
+        <v>91874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819489</v>
+        <v>119819485</v>
       </c>
       <c r="B5" t="n">
-        <v>91463</v>
+        <v>91874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713257</v>
+        <v>713190</v>
       </c>
       <c r="R5" t="n">
-        <v>7163139</v>
+        <v>7163199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819487</v>
+        <v>119819477</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713218</v>
+        <v>713041</v>
       </c>
       <c r="R6" t="n">
-        <v>7163161</v>
+        <v>7162983</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819477</v>
+        <v>119819484</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713041</v>
+        <v>713213</v>
       </c>
       <c r="R7" t="n">
-        <v>7162983</v>
+        <v>7163095</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819482</v>
+        <v>119819479</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713088</v>
+        <v>713072</v>
       </c>
       <c r="R8" t="n">
-        <v>7163047</v>
+        <v>7163032</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819484</v>
+        <v>119819489</v>
       </c>
       <c r="B9" t="n">
-        <v>91856</v>
+        <v>91481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713213</v>
+        <v>713257</v>
       </c>
       <c r="R9" t="n">
-        <v>7163095</v>
+        <v>7163139</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819485</v>
+        <v>119819491</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
+        <v>89269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713190</v>
+        <v>713241</v>
       </c>
       <c r="R10" t="n">
-        <v>7163199</v>
+        <v>7163150</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819481</v>
+        <v>119819486</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,30 +1686,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713079</v>
+        <v>713196</v>
       </c>
       <c r="R11" t="n">
-        <v>7163036</v>
+        <v>7163164</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819490</v>
+        <v>119819487</v>
       </c>
       <c r="B12" t="n">
-        <v>89252</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713250</v>
+        <v>713218</v>
       </c>
       <c r="R12" t="n">
-        <v>7163149</v>
+        <v>7163161</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819479</v>
+        <v>119819482</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713072</v>
+        <v>713088</v>
       </c>
       <c r="R13" t="n">
-        <v>7163032</v>
+        <v>7163047</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819491</v>
+        <v>119819483</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
+        <v>91874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713241</v>
+        <v>713186</v>
       </c>
       <c r="R14" t="n">
-        <v>7163150</v>
+        <v>7163050</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 32609-2019 artfynd.xlsx
+++ b/artfynd/A 32609-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819481</v>
+        <v>119819486</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713079</v>
+        <v>713196</v>
       </c>
       <c r="R2" t="n">
-        <v>7163036</v>
+        <v>7163164</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819490</v>
+        <v>119819477</v>
       </c>
       <c r="B3" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713250</v>
+        <v>713041</v>
       </c>
       <c r="R3" t="n">
-        <v>7163149</v>
+        <v>7162983</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819478</v>
+        <v>119819489</v>
       </c>
       <c r="B4" t="n">
-        <v>91874</v>
+        <v>91481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713071</v>
+        <v>713257</v>
       </c>
       <c r="R4" t="n">
-        <v>7163031</v>
+        <v>7163139</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819485</v>
+        <v>119819487</v>
       </c>
       <c r="B5" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713190</v>
+        <v>713218</v>
       </c>
       <c r="R5" t="n">
-        <v>7163199</v>
+        <v>7163161</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819477</v>
+        <v>119819478</v>
       </c>
       <c r="B6" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713041</v>
+        <v>713071</v>
       </c>
       <c r="R6" t="n">
-        <v>7162983</v>
+        <v>7163031</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819484</v>
+        <v>119819491</v>
       </c>
       <c r="B7" t="n">
-        <v>91874</v>
+        <v>89269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713213</v>
+        <v>713241</v>
       </c>
       <c r="R7" t="n">
-        <v>7163095</v>
+        <v>7163150</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819479</v>
+        <v>119819481</v>
       </c>
       <c r="B8" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,26 +1357,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713072</v>
+        <v>713079</v>
       </c>
       <c r="R8" t="n">
-        <v>7163032</v>
+        <v>7163036</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819489</v>
+        <v>119819479</v>
       </c>
       <c r="B9" t="n">
-        <v>91481</v>
+        <v>91874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713257</v>
+        <v>713072</v>
       </c>
       <c r="R9" t="n">
-        <v>7163139</v>
+        <v>7163032</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819491</v>
+        <v>119819485</v>
       </c>
       <c r="B10" t="n">
-        <v>89269</v>
+        <v>91874</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713241</v>
+        <v>713190</v>
       </c>
       <c r="R10" t="n">
-        <v>7163150</v>
+        <v>7163199</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819486</v>
+        <v>119819482</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713196</v>
+        <v>713088</v>
       </c>
       <c r="R11" t="n">
-        <v>7163164</v>
+        <v>7163047</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819487</v>
+        <v>119819483</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713218</v>
+        <v>713186</v>
       </c>
       <c r="R12" t="n">
-        <v>7163161</v>
+        <v>7163050</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819482</v>
+        <v>119819490</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713088</v>
+        <v>713250</v>
       </c>
       <c r="R13" t="n">
-        <v>7163047</v>
+        <v>7163149</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819483</v>
+        <v>119819484</v>
       </c>
       <c r="B14" t="n">
         <v>91874</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713186</v>
+        <v>713213</v>
       </c>
       <c r="R14" t="n">
-        <v>7163050</v>
+        <v>7163095</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 32609-2019 artfynd.xlsx
+++ b/artfynd/A 32609-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819486</v>
+        <v>119819482</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713196</v>
+        <v>713088</v>
       </c>
       <c r="R2" t="n">
-        <v>7163164</v>
+        <v>7163047</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819489</v>
+        <v>119819484</v>
       </c>
       <c r="B4" t="n">
-        <v>91481</v>
+        <v>91874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713257</v>
+        <v>713213</v>
       </c>
       <c r="R4" t="n">
-        <v>7163139</v>
+        <v>7163095</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819487</v>
+        <v>119819483</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713218</v>
+        <v>713186</v>
       </c>
       <c r="R5" t="n">
-        <v>7163161</v>
+        <v>7163050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819478</v>
+        <v>119819481</v>
       </c>
       <c r="B6" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713071</v>
+        <v>713079</v>
       </c>
       <c r="R6" t="n">
-        <v>7163031</v>
+        <v>7163036</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819491</v>
+        <v>119819479</v>
       </c>
       <c r="B7" t="n">
-        <v>89269</v>
+        <v>91874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713241</v>
+        <v>713072</v>
       </c>
       <c r="R7" t="n">
-        <v>7163150</v>
+        <v>7163032</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819481</v>
+        <v>119819487</v>
       </c>
       <c r="B8" t="n">
         <v>91852</v>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713079</v>
+        <v>713218</v>
       </c>
       <c r="R8" t="n">
-        <v>7163036</v>
+        <v>7163161</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819479</v>
+        <v>119819486</v>
       </c>
       <c r="B9" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713072</v>
+        <v>713196</v>
       </c>
       <c r="R9" t="n">
-        <v>7163032</v>
+        <v>7163164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819482</v>
+        <v>119819478</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713088</v>
+        <v>713071</v>
       </c>
       <c r="R11" t="n">
-        <v>7163047</v>
+        <v>7163031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819483</v>
+        <v>119819490</v>
       </c>
       <c r="B12" t="n">
-        <v>91874</v>
+        <v>89269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713186</v>
+        <v>713250</v>
       </c>
       <c r="R12" t="n">
-        <v>7163050</v>
+        <v>7163149</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819490</v>
+        <v>119819489</v>
       </c>
       <c r="B13" t="n">
-        <v>89269</v>
+        <v>91481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>4745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713250</v>
+        <v>713257</v>
       </c>
       <c r="R13" t="n">
-        <v>7163149</v>
+        <v>7163139</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819484</v>
+        <v>119819491</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
+        <v>89269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713213</v>
+        <v>713241</v>
       </c>
       <c r="R14" t="n">
-        <v>7163095</v>
+        <v>7163150</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
